--- a/artfynd/A 28241-2024 artfynd.xlsx
+++ b/artfynd/A 28241-2024 artfynd.xlsx
@@ -2493,10 +2493,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118663519</v>
+        <v>118663420</v>
       </c>
       <c r="B18" t="n">
-        <v>90524</v>
+        <v>94620</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,38 +2505,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2544,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579920</v>
+        <v>579904</v>
       </c>
       <c r="R18" t="n">
-        <v>6398869</v>
+        <v>6398889</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2607,10 +2600,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118663420</v>
+        <v>118663519</v>
       </c>
       <c r="B19" t="n">
-        <v>94620</v>
+        <v>90524</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2619,31 +2612,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579904</v>
+        <v>579920</v>
       </c>
       <c r="R19" t="n">
-        <v>6398889</v>
+        <v>6398869</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 28241-2024 artfynd.xlsx
+++ b/artfynd/A 28241-2024 artfynd.xlsx
@@ -1053,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118281645</v>
+        <v>118281710</v>
       </c>
       <c r="B5" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,46 +1065,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 28241, Stormandebo, Sm</t>
+          <t>A 28241, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580054</v>
+        <v>579904</v>
       </c>
       <c r="R5" t="n">
-        <v>6398984</v>
+        <v>6398804</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1145,6 +1145,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1163,10 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118281756</v>
+        <v>118281694</v>
       </c>
       <c r="B6" t="n">
-        <v>57443</v>
+        <v>94620</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,39 +1176,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1215,13 +1208,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580056</v>
+        <v>579981</v>
       </c>
       <c r="R6" t="n">
-        <v>6398942</v>
+        <v>6398780</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,6 +1252,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1277,7 +1271,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118282018</v>
+        <v>118281798</v>
       </c>
       <c r="B7" t="n">
         <v>97846</v>
@@ -1325,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579904</v>
+        <v>579888</v>
       </c>
       <c r="R7" t="n">
-        <v>6398804</v>
+        <v>6398839</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118281694</v>
+        <v>118281756</v>
       </c>
       <c r="B8" t="n">
-        <v>94620</v>
+        <v>57443</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1400,31 +1394,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1432,13 +1434,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579981</v>
+        <v>580056</v>
       </c>
       <c r="R8" t="n">
-        <v>6398780</v>
+        <v>6398942</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,7 +1478,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1495,10 +1496,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118281834</v>
+        <v>118281645</v>
       </c>
       <c r="B9" t="n">
-        <v>90524</v>
+        <v>57306</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,34 +1512,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1546,10 +1544,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579844</v>
+        <v>580054</v>
       </c>
       <c r="R9" t="n">
-        <v>6398856</v>
+        <v>6398984</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,7 +1588,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1609,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118281798</v>
+        <v>118281834</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,35 +1618,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579888</v>
+        <v>579844</v>
       </c>
       <c r="R10" t="n">
-        <v>6398839</v>
+        <v>6398856</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1945,7 +1945,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118352272</v>
+        <v>118352290</v>
       </c>
       <c r="B13" t="n">
         <v>90524</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580024</v>
+        <v>579914</v>
       </c>
       <c r="R13" t="n">
-        <v>6398880</v>
+        <v>6398887</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118352290</v>
+        <v>118352311</v>
       </c>
       <c r="B14" t="n">
         <v>90524</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579914</v>
+        <v>580019</v>
       </c>
       <c r="R14" t="n">
-        <v>6398887</v>
+        <v>6398874</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118352311</v>
+        <v>118352272</v>
       </c>
       <c r="B15" t="n">
         <v>90524</v>
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580019</v>
+        <v>580024</v>
       </c>
       <c r="R15" t="n">
-        <v>6398874</v>
+        <v>6398880</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118663303</v>
+        <v>118663441</v>
       </c>
       <c r="B16" t="n">
-        <v>94620</v>
+        <v>97846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,30 +2287,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2319,10 +2327,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579808</v>
+        <v>579904</v>
       </c>
       <c r="R16" t="n">
-        <v>6398876</v>
+        <v>6398901</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2382,10 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118663479</v>
+        <v>118663303</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>94620</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2394,33 +2402,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2430,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579913</v>
+        <v>579808</v>
       </c>
       <c r="R17" t="n">
-        <v>6398901</v>
+        <v>6398876</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2493,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118663420</v>
+        <v>118663491</v>
       </c>
       <c r="B18" t="n">
-        <v>94620</v>
+        <v>97846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,30 +2509,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2537,10 +2549,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579904</v>
+        <v>579909</v>
       </c>
       <c r="R18" t="n">
-        <v>6398889</v>
+        <v>6398911</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2600,7 +2612,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118663519</v>
+        <v>118663550</v>
       </c>
       <c r="B19" t="n">
         <v>90524</v>
@@ -2651,10 +2663,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579920</v>
+        <v>579957</v>
       </c>
       <c r="R19" t="n">
-        <v>6398869</v>
+        <v>6398759</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2714,7 +2726,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118663491</v>
+        <v>118663479</v>
       </c>
       <c r="B20" t="n">
         <v>97846</v>
@@ -2753,11 +2765,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2766,10 +2774,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579909</v>
+        <v>579913</v>
       </c>
       <c r="R20" t="n">
-        <v>6398911</v>
+        <v>6398901</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2829,10 +2837,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118663441</v>
+        <v>118663420</v>
       </c>
       <c r="B21" t="n">
-        <v>97846</v>
+        <v>94620</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2841,38 +2849,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2884,7 +2884,7 @@
         <v>579904</v>
       </c>
       <c r="R21" t="n">
-        <v>6398901</v>
+        <v>6398889</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2944,7 +2944,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118663550</v>
+        <v>118663519</v>
       </c>
       <c r="B22" t="n">
         <v>90524</v>
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579957</v>
+        <v>579920</v>
       </c>
       <c r="R22" t="n">
-        <v>6398759</v>
+        <v>6398869</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 28241-2024 artfynd.xlsx
+++ b/artfynd/A 28241-2024 artfynd.xlsx
@@ -1053,7 +1053,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118281710</v>
+        <v>118281667</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1097,14 +1097,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 28241, Sm</t>
+          <t>A 28241, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579904</v>
+        <v>580096</v>
       </c>
       <c r="R5" t="n">
-        <v>6398804</v>
+        <v>6398980</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118281694</v>
+        <v>118281947</v>
       </c>
       <c r="B6" t="n">
-        <v>94620</v>
+        <v>90524</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,31 +1176,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1208,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579981</v>
+        <v>580029</v>
       </c>
       <c r="R6" t="n">
-        <v>6398780</v>
+        <v>6398869</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1271,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118281798</v>
+        <v>118281834</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,35 +1290,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1319,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579888</v>
+        <v>579844</v>
       </c>
       <c r="R7" t="n">
-        <v>6398839</v>
+        <v>6398856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118281756</v>
+        <v>118281645</v>
       </c>
       <c r="B8" t="n">
-        <v>57443</v>
+        <v>57306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,33 +1408,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1434,13 +1440,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580056</v>
+        <v>580054</v>
       </c>
       <c r="R8" t="n">
-        <v>6398942</v>
+        <v>6398984</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1496,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118281645</v>
+        <v>118281798</v>
       </c>
       <c r="B9" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,35 +1514,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1544,10 +1550,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580054</v>
+        <v>579888</v>
       </c>
       <c r="R9" t="n">
-        <v>6398984</v>
+        <v>6398839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,6 +1594,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1606,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118281834</v>
+        <v>118281756</v>
       </c>
       <c r="B10" t="n">
-        <v>90524</v>
+        <v>57443</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,34 +1629,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1657,13 +1665,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579844</v>
+        <v>580056</v>
       </c>
       <c r="R10" t="n">
-        <v>6398856</v>
+        <v>6398942</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1701,7 +1709,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1720,7 +1727,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118281667</v>
+        <v>118281710</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1764,14 +1771,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 28241, Stormandebo, Sm</t>
+          <t>A 28241, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580096</v>
+        <v>579904</v>
       </c>
       <c r="R11" t="n">
-        <v>6398980</v>
+        <v>6398804</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1831,10 +1838,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118281947</v>
+        <v>118281694</v>
       </c>
       <c r="B12" t="n">
-        <v>90524</v>
+        <v>94620</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,38 +1850,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580029</v>
+        <v>579981</v>
       </c>
       <c r="R12" t="n">
-        <v>6398869</v>
+        <v>6398780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1945,7 +1945,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118352290</v>
+        <v>118352311</v>
       </c>
       <c r="B13" t="n">
         <v>90524</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579914</v>
+        <v>580019</v>
       </c>
       <c r="R13" t="n">
-        <v>6398887</v>
+        <v>6398874</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118352311</v>
+        <v>118352272</v>
       </c>
       <c r="B14" t="n">
         <v>90524</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580019</v>
+        <v>580024</v>
       </c>
       <c r="R14" t="n">
-        <v>6398874</v>
+        <v>6398880</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118352272</v>
+        <v>118352290</v>
       </c>
       <c r="B15" t="n">
         <v>90524</v>
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580024</v>
+        <v>579914</v>
       </c>
       <c r="R15" t="n">
-        <v>6398880</v>
+        <v>6398887</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2275,7 +2275,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118663441</v>
+        <v>118663479</v>
       </c>
       <c r="B16" t="n">
         <v>97846</v>
@@ -2314,11 +2314,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2327,7 +2323,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579904</v>
+        <v>579913</v>
       </c>
       <c r="R16" t="n">
         <v>6398901</v>
@@ -2390,7 +2386,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118663303</v>
+        <v>118663420</v>
       </c>
       <c r="B17" t="n">
         <v>94620</v>
@@ -2434,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579808</v>
+        <v>579904</v>
       </c>
       <c r="R17" t="n">
-        <v>6398876</v>
+        <v>6398889</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2497,7 +2493,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118663491</v>
+        <v>118663441</v>
       </c>
       <c r="B18" t="n">
         <v>97846</v>
@@ -2549,10 +2545,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579909</v>
+        <v>579904</v>
       </c>
       <c r="R18" t="n">
-        <v>6398911</v>
+        <v>6398901</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2612,10 +2608,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118663550</v>
+        <v>118663303</v>
       </c>
       <c r="B19" t="n">
-        <v>90524</v>
+        <v>94620</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,38 +2620,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2663,10 +2652,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579957</v>
+        <v>579808</v>
       </c>
       <c r="R19" t="n">
-        <v>6398759</v>
+        <v>6398876</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2726,10 +2715,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118663479</v>
+        <v>118663550</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2738,35 +2727,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2774,10 +2766,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579913</v>
+        <v>579957</v>
       </c>
       <c r="R20" t="n">
-        <v>6398901</v>
+        <v>6398759</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2837,10 +2829,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118663420</v>
+        <v>118663519</v>
       </c>
       <c r="B21" t="n">
-        <v>94620</v>
+        <v>90524</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2849,31 +2841,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2881,10 +2880,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579904</v>
+        <v>579920</v>
       </c>
       <c r="R21" t="n">
-        <v>6398889</v>
+        <v>6398869</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2944,10 +2943,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118663519</v>
+        <v>118663491</v>
       </c>
       <c r="B22" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2956,38 +2955,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579920</v>
+        <v>579909</v>
       </c>
       <c r="R22" t="n">
-        <v>6398869</v>
+        <v>6398911</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 28241-2024 artfynd.xlsx
+++ b/artfynd/A 28241-2024 artfynd.xlsx
@@ -1948,7 +1948,7 @@
         <v>118352311</v>
       </c>
       <c r="B13" t="n">
-        <v>90524</v>
+        <v>90531</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>118352272</v>
       </c>
       <c r="B14" t="n">
-        <v>90524</v>
+        <v>90531</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>118352290</v>
       </c>
       <c r="B15" t="n">
-        <v>90524</v>
+        <v>90531</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118663479</v>
+        <v>118663519</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>90531</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,35 +2287,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2323,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579913</v>
+        <v>579920</v>
       </c>
       <c r="R16" t="n">
-        <v>6398901</v>
+        <v>6398869</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2386,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118663420</v>
+        <v>118663303</v>
       </c>
       <c r="B17" t="n">
-        <v>94620</v>
+        <v>94627</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,10 +2433,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579904</v>
+        <v>579808</v>
       </c>
       <c r="R17" t="n">
-        <v>6398889</v>
+        <v>6398876</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2493,10 +2496,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118663441</v>
+        <v>118663420</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>94627</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,38 +2508,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2548,7 +2543,7 @@
         <v>579904</v>
       </c>
       <c r="R18" t="n">
-        <v>6398901</v>
+        <v>6398889</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2608,10 +2603,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118663303</v>
+        <v>118663479</v>
       </c>
       <c r="B19" t="n">
-        <v>94620</v>
+        <v>97853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,29 +2615,33 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2652,10 +2651,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579808</v>
+        <v>579913</v>
       </c>
       <c r="R19" t="n">
-        <v>6398876</v>
+        <v>6398901</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2715,10 +2714,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118663550</v>
+        <v>118663441</v>
       </c>
       <c r="B20" t="n">
-        <v>90524</v>
+        <v>97853</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,38 +2726,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579957</v>
+        <v>579904</v>
       </c>
       <c r="R20" t="n">
-        <v>6398759</v>
+        <v>6398901</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118663519</v>
+        <v>118663550</v>
       </c>
       <c r="B21" t="n">
-        <v>90524</v>
+        <v>90531</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579920</v>
+        <v>579957</v>
       </c>
       <c r="R21" t="n">
-        <v>6398869</v>
+        <v>6398759</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2946,7 +2946,7 @@
         <v>118663491</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 28241-2024 artfynd.xlsx
+++ b/artfynd/A 28241-2024 artfynd.xlsx
@@ -1945,7 +1945,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118352311</v>
+        <v>118352272</v>
       </c>
       <c r="B13" t="n">
         <v>90531</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580019</v>
+        <v>580024</v>
       </c>
       <c r="R13" t="n">
-        <v>6398874</v>
+        <v>6398880</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118352272</v>
+        <v>118352311</v>
       </c>
       <c r="B14" t="n">
         <v>90531</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580024</v>
+        <v>580019</v>
       </c>
       <c r="R14" t="n">
-        <v>6398880</v>
+        <v>6398874</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118663519</v>
+        <v>118663303</v>
       </c>
       <c r="B16" t="n">
-        <v>90531</v>
+        <v>94627</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,38 +2287,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2326,10 +2319,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579920</v>
+        <v>579808</v>
       </c>
       <c r="R16" t="n">
-        <v>6398869</v>
+        <v>6398876</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2389,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118663303</v>
+        <v>118663519</v>
       </c>
       <c r="B17" t="n">
-        <v>94627</v>
+        <v>90531</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,31 +2394,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579808</v>
+        <v>579920</v>
       </c>
       <c r="R17" t="n">
-        <v>6398876</v>
+        <v>6398869</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2496,10 +2496,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118663420</v>
+        <v>118663479</v>
       </c>
       <c r="B18" t="n">
-        <v>94627</v>
+        <v>97853</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2508,29 +2508,33 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2540,10 +2544,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579904</v>
+        <v>579913</v>
       </c>
       <c r="R18" t="n">
-        <v>6398889</v>
+        <v>6398901</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2603,10 +2607,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118663479</v>
+        <v>118663420</v>
       </c>
       <c r="B19" t="n">
-        <v>97853</v>
+        <v>94627</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,33 +2619,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579913</v>
+        <v>579904</v>
       </c>
       <c r="R19" t="n">
-        <v>6398901</v>
+        <v>6398889</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 28241-2024 artfynd.xlsx
+++ b/artfynd/A 28241-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72677808</v>
+        <v>74119886</v>
       </c>
       <c r="B3" t="n">
         <v>103226</v>
@@ -835,23 +835,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Koltorp, Sm</t>
+          <t>Koltorp 1000 m S, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579999.0789199262</v>
+        <v>579993.2999020357</v>
       </c>
       <c r="R3" t="n">
-        <v>6398892.915519954</v>
+        <v>6398887.459238708</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +871,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-08-12</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -885,7 +881,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-08-12</t>
+          <t>1988-12-31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -895,42 +891,46 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Orörd skog och lämplig biotop. Tidigare funnen 1985, personen är avliden. Letat ca 100 meter omkring den angivna positionen.</t>
+          <t>Smålands flora 2007: KOO: 7G0g 0120. SOM: Chimaphila umbellata. LEG: Margareta Wester, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrskogssluttning</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Via Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Kärlväxtinventering</t>
+          <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74119886</v>
+        <v>118281667</v>
       </c>
       <c r="B4" t="n">
-        <v>103226</v>
+        <v>97846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,41 +939,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Koltorp 1000 m S, Sm</t>
+          <t>A 28241, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579993.2999020357</v>
+        <v>580096</v>
       </c>
       <c r="R4" t="n">
-        <v>6398887.459238708</v>
+        <v>6398980</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,27 +1005,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 7G0g 0120. SOM: Chimaphila umbellata. LEG: Margareta Wester, Stefan Kasselstrand</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,37 +1019,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrskogssluttning</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118281667</v>
+        <v>118281947</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,35 +1050,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1101,10 +1089,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580096</v>
+        <v>580029</v>
       </c>
       <c r="R5" t="n">
-        <v>6398980</v>
+        <v>6398869</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1164,7 +1152,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118281947</v>
+        <v>118281834</v>
       </c>
       <c r="B6" t="n">
         <v>90524</v>
@@ -1199,7 +1187,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1215,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580029</v>
+        <v>579844</v>
       </c>
       <c r="R6" t="n">
-        <v>6398869</v>
+        <v>6398856</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118281834</v>
+        <v>118281645</v>
       </c>
       <c r="B7" t="n">
-        <v>90524</v>
+        <v>57306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,34 +1282,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1329,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579844</v>
+        <v>580054</v>
       </c>
       <c r="R7" t="n">
-        <v>6398856</v>
+        <v>6398984</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1373,7 +1358,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1392,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118281645</v>
+        <v>118281798</v>
       </c>
       <c r="B8" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,35 +1388,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1440,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580054</v>
+        <v>579888</v>
       </c>
       <c r="R8" t="n">
-        <v>6398984</v>
+        <v>6398839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,6 +1468,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1502,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118281798</v>
+        <v>118281756</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>57443</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,35 +1499,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1550,13 +1539,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579888</v>
+        <v>580056</v>
       </c>
       <c r="R9" t="n">
-        <v>6398839</v>
+        <v>6398942</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1594,7 +1583,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1613,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118281756</v>
+        <v>118281710</v>
       </c>
       <c r="B10" t="n">
-        <v>57443</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,53 +1613,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 28241, Stormandebo, Sm</t>
+          <t>A 28241, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580056</v>
+        <v>579904</v>
       </c>
       <c r="R10" t="n">
-        <v>6398942</v>
+        <v>6398804</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1709,6 +1693,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1727,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118281710</v>
+        <v>118281694</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>94620</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,46 +1724,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 28241, Sm</t>
+          <t>A 28241, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579904</v>
+        <v>579981</v>
       </c>
       <c r="R11" t="n">
-        <v>6398804</v>
+        <v>6398780</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1838,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118281694</v>
+        <v>118352272</v>
       </c>
       <c r="B12" t="n">
-        <v>94620</v>
+        <v>90531</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1850,45 +1831,48 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 28241, Stormandebo, Sm</t>
+          <t>Koltorp_syd, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579981</v>
+        <v>580024</v>
       </c>
       <c r="R12" t="n">
-        <v>6398780</v>
+        <v>6398880</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1912,12 +1896,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,19 +1917,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118352272</v>
+        <v>118352311</v>
       </c>
       <c r="B13" t="n">
         <v>90531</v>
@@ -1992,10 +1976,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580024</v>
+        <v>580019</v>
       </c>
       <c r="R13" t="n">
-        <v>6398880</v>
+        <v>6398874</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2055,7 +2039,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118352311</v>
+        <v>118352290</v>
       </c>
       <c r="B14" t="n">
         <v>90531</v>
@@ -2102,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580019</v>
+        <v>579914</v>
       </c>
       <c r="R14" t="n">
-        <v>6398874</v>
+        <v>6398887</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2165,10 +2149,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118352290</v>
+        <v>118663519</v>
       </c>
       <c r="B15" t="n">
-        <v>90531</v>
+        <v>90533</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2203,22 +2187,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Koltorp_syd, Sm</t>
+          <t>A 28241, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579914</v>
+        <v>579920</v>
       </c>
       <c r="R15" t="n">
-        <v>6398887</v>
+        <v>6398869</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2242,12 +2230,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,22 +2251,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118663519</v>
+        <v>118663479</v>
       </c>
       <c r="B16" t="n">
-        <v>90533</v>
+        <v>97858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,38 +2275,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2326,10 +2311,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579920</v>
+        <v>579913</v>
       </c>
       <c r="R16" t="n">
-        <v>6398869</v>
+        <v>6398901</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2389,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118663479</v>
+        <v>118663550</v>
       </c>
       <c r="B17" t="n">
-        <v>97858</v>
+        <v>90533</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,35 +2386,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2437,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579913</v>
+        <v>579957</v>
       </c>
       <c r="R17" t="n">
-        <v>6398901</v>
+        <v>6398759</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2500,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118663550</v>
+        <v>118663420</v>
       </c>
       <c r="B18" t="n">
-        <v>90533</v>
+        <v>94632</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2512,38 +2500,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2551,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579957</v>
+        <v>579904</v>
       </c>
       <c r="R18" t="n">
-        <v>6398759</v>
+        <v>6398889</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,10 +2595,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118663420</v>
+        <v>118663491</v>
       </c>
       <c r="B19" t="n">
-        <v>94632</v>
+        <v>97858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2626,30 +2607,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2658,10 +2647,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579904</v>
+        <v>579909</v>
       </c>
       <c r="R19" t="n">
-        <v>6398889</v>
+        <v>6398911</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2721,7 +2710,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118663491</v>
+        <v>118663441</v>
       </c>
       <c r="B20" t="n">
         <v>97858</v>
@@ -2773,10 +2762,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579909</v>
+        <v>579904</v>
       </c>
       <c r="R20" t="n">
-        <v>6398911</v>
+        <v>6398901</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2836,10 +2825,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118663441</v>
+        <v>118663303</v>
       </c>
       <c r="B21" t="n">
-        <v>97858</v>
+        <v>94632</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,38 +2837,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2888,10 +2869,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579904</v>
+        <v>579808</v>
       </c>
       <c r="R21" t="n">
-        <v>6398901</v>
+        <v>6398876</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2951,10 +2932,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118663303</v>
+        <v>119181311</v>
       </c>
       <c r="B22" t="n">
-        <v>94632</v>
+        <v>91838</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2967,41 +2948,48 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 28241, Stormbo, Sm</t>
+          <t>A 28241, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579808</v>
+        <v>579800</v>
       </c>
       <c r="R22" t="n">
-        <v>6398876</v>
+        <v>6398883</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3025,12 +3013,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,14 +3039,14 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119181311</v>
+        <v>119180670</v>
       </c>
       <c r="B23" t="n">
         <v>91838</v>
@@ -3093,7 +3081,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3105,17 +3093,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 28241, Ankarsrum, Sm</t>
+          <t>A 28241, Ankarsum, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579800</v>
+        <v>579915</v>
       </c>
       <c r="R23" t="n">
-        <v>6398883</v>
+        <v>6398928</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3172,10 +3160,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119180670</v>
+        <v>119180809</v>
       </c>
       <c r="B24" t="n">
-        <v>91838</v>
+        <v>97905</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3184,49 +3172,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 28241, Ankarsum, Sm</t>
+          <t>A 28241, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579915</v>
+        <v>579909</v>
       </c>
       <c r="R24" t="n">
-        <v>6398928</v>
+        <v>6398898</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3286,7 +3271,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119180809</v>
+        <v>119180735</v>
       </c>
       <c r="B25" t="n">
         <v>97905</v>
@@ -3334,10 +3319,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579909</v>
+        <v>579911</v>
       </c>
       <c r="R25" t="n">
-        <v>6398898</v>
+        <v>6398906</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3397,7 +3382,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119180735</v>
+        <v>119180771</v>
       </c>
       <c r="B26" t="n">
         <v>97905</v>
@@ -3431,11 +3416,7 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3445,10 +3426,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>579911</v>
+        <v>579904</v>
       </c>
       <c r="R26" t="n">
-        <v>6398906</v>
+        <v>6398894</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3508,7 +3489,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119180771</v>
+        <v>119180834</v>
       </c>
       <c r="B27" t="n">
         <v>97905</v>
@@ -3552,10 +3533,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579904</v>
+        <v>579921</v>
       </c>
       <c r="R27" t="n">
-        <v>6398894</v>
+        <v>6398921</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3615,10 +3596,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119180834</v>
+        <v>119180691</v>
       </c>
       <c r="B28" t="n">
-        <v>97905</v>
+        <v>57461</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3627,31 +3608,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3659,13 +3648,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579921</v>
+        <v>579915</v>
       </c>
       <c r="R28" t="n">
-        <v>6398921</v>
+        <v>6398928</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3703,7 +3692,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3719,120 +3707,6 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>119180691</v>
-      </c>
-      <c r="B29" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>A 28241, Ankarsrum, Sm</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>579915</v>
-      </c>
-      <c r="R29" t="n">
-        <v>6398928</v>
-      </c>
-      <c r="S29" t="n">
-        <v>25</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Hallingeberg</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2024-08-17</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2024-08-17</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
